--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -428,7 +428,7 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>直接按人民币金额结算；本版按已确认的原标准等值换算，日常登记不再使用积分。</t>
+          <t>2026-09-14修订：人民币直接计酬，任务单价不变；广告成果可累计升级补差。</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>同Campaign同轮只取最高档；升级仅补已结算差额。受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并；复盘、升级不算新次数。同一成果不跨周重领，也不再凭同一效果领取成果奖金。详见广告优化规则。</t>
+          <t>同Campaign同轮只取最高档；受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并，复盘和升级不算新次数。同一成果不跨周重领。广告任务与成果奖按同案累计总额补差，详见广告优化规则。</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>同Campaign同轮只取最高档；升级仅补已结算差额。受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并；复盘、升级不算新次数。同一成果不跨周重领，也不再凭同一效果领取成果奖金。详见广告优化规则。</t>
+          <t>同Campaign同轮只取最高档；受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并，复盘和升级不算新次数。同一成果不跨周重领。广告任务与成果奖按同案累计总额补差，详见广告优化规则。</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>同Campaign同轮只取最高档；升级仅补已结算差额。受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并；复盘、升级不算新次数。同一成果不跨周重领，也不再凭同一效果领取成果奖金。详见广告优化规则。</t>
+          <t>同Campaign同轮只取最高档；受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并，复盘和升级不算新次数。同一成果不跨周重领。广告任务与成果奖按同案累计总额补差，详见广告优化规则。</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>同Campaign同轮只取最高档；升级仅补已结算差额。受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并；复盘、升级不算新次数。同一成果不跨周重领，也不再凭同一效果领取成果奖金。详见广告优化规则。</t>
+          <t>同Campaign同轮只取最高档；受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并，复盘和升级不算新次数。同一成果不跨周重领。广告任务与成果奖按同案累计总额补差，详见广告优化规则。</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>同Campaign同轮只取最高档；升级仅补已结算差额。受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并；复盘、升级不算新次数。同一成果不跨周重领，也不再凭同一效果领取成果奖金。详见广告优化规则。</t>
+          <t>同Campaign同轮只取最高档；受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并，复盘和升级不算新次数。同一成果不跨周重领。广告任务与成果奖按同案累计总额补差，详见广告优化规则。</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>同Campaign同轮只取最高档；升级仅补已结算差额。受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并；复盘、升级不算新次数。同一成果不跨周重领，也不再凭同一效果领取成果奖金。详见广告优化规则。</t>
+          <t>同Campaign同轮只取最高档；受派/主动均×1，每自然周最多2次有效调整，跨人员与来源合并，复盘和升级不算新次数。同一成果不跨周重领。广告任务与成果奖按同案累计总额补差，详见广告优化规则。</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>跟卖情况检查（是否保留待确认）</t>
+          <t>跟卖情况检查（未启用）</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>按约定清单完成一周人工跟卖检查并记录结果。</t>
+          <t>本项未启用，不自动生成应付报酬。正式启用时确认清单、责任人、频次和生效日期。</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>不按发现数量加价；独立案件处理另按实际交付，无人工工作的自动监控不计人工报酬。</t>
+          <t>5元/周仅为保留价格；启用前不计费。任务金额存在不代表已经批准执行或结算。</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
@@ -6446,7 +6446,7 @@
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>广告同一效果高档金额与现金成果奖互斥；研发产品的独立运营改善可奖励。</t>
+          <t>广告同案可由任务档升级至100元、累计300元成果档，只补差额；非广告的独立任务报酬与成果奖励仍可同时领取。</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>同一成果首次达到本档，核定100元；未验收不提前发放。</t>
+          <t>符合条件首次核定100元；非广告按独立成果奖支付。广告按同案累计总额扣全部历史已付，只补差额。</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>300元为该案例本档总奖励；已发100元则本次只补200元，不另发300元。</t>
+          <t>300元为成果奖累计档位。非广告已领成果奖100元则补200元；广告同案累计应付300元，扣同案全部历史已付后补差。</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>由负责人另行确定案例总奖励。金额未确定不结算；如有此前奖励，按批准总额扣除累计已奖励金额。</t>
+          <t>负责人确定案例总奖励并记录范围；非广告扣已付成果奖，广告按同案累计较高总額减同案全部已付，只结正差额。</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>同成果只取最高核定现金总额，跨月累计补差，不乘主动倍率。研发提成与独立运营贡献可并存。</t>
+          <t>同一成果升级只结正差额，不乘主动倍率。广告适用统一案例累计总额规则；非广告独立任务报酬与成果奖仍可并存。</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>先检查同一效果是否已按广告优化40/50/75元档结算，已结算不重复领现金成果奖。若之前已领现金成果奖，同一效果不再补领广告成果档；实际独立执行报酬可按对应低档验收。新独立成果另认定。</t>
+          <t>广告同一案例按累计总额升级：累计应付取广告任务档金额与已核定成果奖总额中的较高者，不相加；本次支付＝累计应付减同案全部历史已付金额的正差额。历史已付含创建、执行、优化及成果奖励。先领哪一项不影响最终总额。多人共享案例总额，不按人重复领取。</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
     </row>
-    <row r="18" ht="85" customHeight="1">
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>跨月与升级</t>
@@ -6718,14 +6718,14 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>已奖励金额跨月累计，不能换月份或任务编号重新领取。按本次核定总奖励减去累计已奖励金额的正差额结算；无新增核定差额则不发放。</t>
+          <t>非广告成果奖：核定成果奖累计总额减历史成果奖。广告案例：取广告档与核定成果奖累计总额的较高者，减同案创建、执行、优化和奖金等全部已付金额。无正差额不支付。</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
     </row>
-    <row r="19" ht="165" customHeight="1">
+    <row r="19" ht="195" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>任务与成果边界</t>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>任务通过验收可先按任务报酬结算；效果仍待观察不阻止已完成任务的结算。成果未达到目标不自动追扣合格任务报酬；修复本人错误或无依据操作不作为新成果奖励。 责任以操作当时已确认资料及执行证据为准；本人开发缺陷、本人执行错误的补救均不另计报酬或成果奖，不能通过更新资料或新建任务转为新成果。资料后续更新及证据不足的处理，详见“优化登记与复盘规则”。</t>
+          <t>任务通过验收可先按任务报酬结算；效果仍待观察不阻止已完成任务的结算。成果未达到目标不自动追扣合格任务报酬；修复本人错误或无依据操作不作为新成果奖励。 责任以操作当时已确认资料及执行证据为准；本人开发缺陷、本人执行错误的补救均不另计报酬或成果奖，不能通过更新资料或新建任务转为新成果。资料后续更新及证据不足的处理，详见“优化登记与复盘规则”。 广告同案采用累计总额补差例外，不将任务报酬与成果奖全额相加。</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -6969,7 +6969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G25"/>
+  <dimension ref="A2:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>单位金额（元）</t>
+          <t>单位/累计金额（元）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>数量/份额</t>
+          <t>数量/份额/历史已付</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -7590,6 +7590,96 @@
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>满足主动分析、实质制作及复盘条件，总报酬50元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="85" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>广告75元升级100元</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>同案补差</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8">
+        <f>MAX(0,C26-D26)*E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>累计100元－历史已付75元＝本次25元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="85" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>广告100元升级300元</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>同案补差</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <f>MAX(0,C27-D27)*E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>累计300元－历史已付100元＝本次200元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="85" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>先领成果100元后核广告75元</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>同案补差</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8">
+        <f>MAX(0,C28-D28)*E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>累计较高值100元，历史已付100元，不再付款。</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7734,7 @@
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>同一交付只结算一次乘倍率后的金额；广告方案内创建与调整按专项互斥。</t>
+          <t>同一交付只结算一次乘倍率后的金额；广告同案奖励按累计总额补差，详见广告优化规则。</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7816,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>受派、主动均固定×1。同Campaign同轮最高75元，升级只补差额；每自然周最多2次有效调整，跨人员、来源合并。同一成果不跨周重领，不重复领取同效果成果奖金。详见广告优化规则。</t>
+          <t>受派、主动均×1。广告任务档同Campaign同轮最高75元；每自然周最多2次有效调整，跨人员/来源合并。另达成果奖标准时，可升级到同案累计100元或300元，只补差额，不能重复相加。</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D23"/>
+  <dimension ref="A2:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11178,7 +11268,7 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>同一效果已领取40/50/75元档，不再领取现金成果奖；如先领现金成果奖，同一效果也不再补领广告成果档。独立实际执行可按对应低档验收，不重复奖励同一结果。多人分配同一案例总报酬。</t>
+          <t>广告同一案例按累计总额升级：累计应付取广告任务档金额与已核定成果奖总额中的较高者，不相加；本次支付＝累计应付减同案全部历史已付金额的正差额。历史已付含创建、执行、优化及成果奖励。先领哪一项不影响最终总额。多人共享案例总额，不按人重复领取。</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11286,43 @@
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>账户、站点、Campaign ID、任务/案例ID、轮次ID、发起来源、执行人及分工、执行日期及时区、问题及方案、Ads Change、前后数据及观察门槛、实际结果、核定档位、累计已结算金额、本次补差、验收人和日期、关联成果奖励。</t>
+          <t>账户、站点、Campaign ID、任务/案例ID、轮次ID、发起来源、执行人及分工、执行日期及时区、问题及方案、Ads Change、前后数据及观察门槛、实际结果、核定档位、累计已结算金额、本次补差、验收人和日期、关联成果奖励。 同案历史已付包含各类报酬与奖金，使用统一案例编号归集。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>验收目标模板</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>执行前记录：案例ID、基准起止日、观察起止日、基准订单/销售额/花费/ACOS、目标订单或销售额、ACOS上限、允许销售下降范围、持续验证期、样本充分性判断及确认人。按产品填写，未确定门槛不直接核高档。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="85" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>补差示例</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>已付75元，成果获批累计100元，补25元；再升级累计300元，补200元。若先付100元，后核定广告75元，不再付款。未达成果奖标准，仍按广告已验收任务档结算。</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12553,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>任务金额按真实来源和主动改善评价计算；本人责任0元。普通任务与主动任务不重复结算。现金成果奖励另按改善成果奖励，广告已按同一效果取得40/50/75元不再重复领现金成果奖。</t>
+          <t>按任务报酬和主动改善评价计算，责任纠错不付报酬。广告同一案例的任务档与成果奖可升级，累计取较高总额、扣全部已付后补差。非广告独立任务与成果奖可并存。</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F22"/>
+  <dimension ref="A2:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12664,7 +12790,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="85" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>RD01</t>
@@ -12690,7 +12816,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>立项确定一个技术问题、范围、交付和验证方法，参考总报酬250元。资料调查、拆解、分析及试验是该任务的节点，不各自再领完整任务价。一个项目确有多个独立技术问题可分别立项；明显更复杂的任务在开始前另定总金额。无突破但有可靠证据及结论，也可验收研究工作。</t>
+          <t>立项确定一个技术问题、范围、交付和验证方法，参考总报酬250元。资料调查、拆解、分析及试验是该任务的节点，不各自再领完整任务价。一个项目确有多个独立技术问题可分别立项；明显更复杂的任务在开始前另定总金额。无突破但有可靠证据及结论，也可验收研究工作。 250元不作为任务上限。定价依据包括现有资料、技术不确定性、验证路线及轮次、独立交付和预计有效投入；不按等待时间或事后自报天数直接加钱。范围实质增加时先确认新增节点和金额。</t>
         </is>
       </c>
     </row>
@@ -13091,6 +13217,62 @@
       <c r="F22" s="8" t="inlineStr">
         <is>
           <t>项目及任务ID、研究问题、技术目标、交付/验证方法、研究总报酬及节点分配、检查日期、成员份额、突破及投产目标、验收记录、已结算金额。提成另记参数确认和结算记录。 本月应付研究报酬及突破/投产奖金＝已验收累计应付总额减去历史已付金额，只结正差额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="85" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>RD16</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>立项金额确认模板</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>开始前填写</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>项目ID、独立技术问题、已有资料、需验证的假设、计划验证路线、各节点交付及金额、预计有效投入、检查日期、突破指标及奖金、成员份额、批准人及日期。普通调研和技术研究边界按实际交付判断，不重复领取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>RD17</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>阶段工作如何拆</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>可按实际技术问题安排权利信息调查、拆机及原理分析、零部件适配验证、改型设计验证。它们可以是一个任务的多个节点，也可能是独立任务；立项先明确，不能看到阶段名称就分别领取250元。有效排除路线可验收研究报酬，未达到独立突破指标不发突破奖。</t>
         </is>
       </c>
     </row>
@@ -13105,7 +13287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D21"/>
+  <dimension ref="A2:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13202,7 +13384,7 @@
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>待项目确认</t>
+          <t>未启用；待项目确认</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -13220,7 +13402,7 @@
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>待项目确认</t>
+          <t>未启用；待项目确认</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -13238,7 +13420,7 @@
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>待项目确认</t>
+          <t>未启用；待项目确认</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -13424,6 +13606,96 @@
       <c r="D21" s="4" t="inlineStr">
         <is>
           <t>本表为规则及月底统计需求，尚未修改Streamlit、未连接OA或Ads Change。需找到实际项目代码及数据接口后实现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="85" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>验收与跨月归属</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>按验收通过月份计入应付。周任务跨月按该周验收月结算一次；内容复盘或研发节点跨月按各自约定验收节点归属，不按创建日或操作日重复计算。已核定但漏付的历史金额列补发，并保留原验收月份。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="85" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>升级与月度锁定</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>升级确认月只计补差。月底锁定后更正留补差记录，关联原案例、原结算及原因；不得覆盖历史记录后重复领取。任务金额调整只用于确认生效后的范围，原已结算金额不自动重算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>金额精度与多人分配</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>每个案例本次应付四舍五入至人民币分；多人按事前确认份额分配。前面人员四舍五入保留两位，指定最后一人领取本次总额减其他人员之和的余额，确保合计相等。份额合计100%；同一案例中途变更按剩余未付部分另确认，不重算已付。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="85" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>待启用项目</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>P053跟卖检查未启用；销售提成未启用。启用前确认必要参数、责任人、适用对象及生效日期。空白不是0费率，也不能自动采用建议值计算应付；已确认的任务报酬不受提成待定影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="85" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>计算与读取</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>实现要求</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>读取Excel公式不能把空缓存当0元。结算程序按金额、数量、倍率和已付金额重新计算，校验来源及公式结果；缺失参数或结果列待核实。输出保存计算结果，金额保留两位小数。</t>
         </is>
       </c>
     </row>

--- a/亚马逊运营考核_优化版.xlsx
+++ b/亚马逊运营考核_优化版.xlsx
@@ -12712,7 +12712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F24"/>
+  <dimension ref="A2:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12733,14 +12733,14 @@
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>技术研发：研究报酬＋突破额外奖金＋投产奖金＋销售提成；普通新品开发各独立交付仍按50元。</t>
+          <t>技术研发：研究阶段报酬＋突破额外奖金＋投产奖金＋销售提成；普通新品开发各独立交付仍按50元。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>研究250元/独立任务、突破500元/独立目标、投产500元/独立项目，均为立项参考；不是整个研发项目的固定总价。</t>
+          <t>研究阶段250元、技术突破额外500元、投产验收额外500元为三种独立计酬单位，按通用标准执行。不是整个研发项目的固定总价。</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>研究任务报酬</t>
+          <t>研究阶段报酬</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -12806,17 +12806,17 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>元/独立研究任务</t>
+          <t>元/独立研究阶段</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>试行参考；立项确认具体总报酬</t>
+          <t>通用标准</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>立项确定一个技术问题、范围、交付和验证方法，参考总报酬250元。资料调查、拆解、分析及试验是该任务的节点，不各自再领完整任务价。一个项目确有多个独立技术问题可分别立项；明显更复杂的任务在开始前另定总金额。无突破但有可靠证据及结论，也可验收研究工作。 250元不作为任务上限。定价依据包括现有资料、技术不确定性、验证路线及轮次、独立交付和预计有效投入；不按等待时间或事后自报天数直接加钱。范围实质增加时先确认新增节点和金额。</t>
+          <t>有实际调查、拆解、设计或试验记录，形成有依据的结论和下一步建议；结论为不可行也可以验收。按实际交付划分阶段，不按周数、试验次数或SKU数量计费。一个项目确有多个独立研究阶段可分别计酬。仅查一下资料或联系一家供应商，不算完成一个研究阶段。250元不作为阶段上限；明显更复杂的阶段在开始前另定金额。定价依据包括现有资料、技术不确定性、验证路线及轮次、独立交付和预计有效投入；不按等待时间或事后自报天数直接加钱。范围实质增加时先确认新增节点和金额。</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>阶段突破额外奖金</t>
+          <t>技术突破奖金</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -12836,17 +12836,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>元/独立突破目标</t>
+          <t>元/独立技术难点</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>试行参考；立项确认指标及总报酬</t>
+          <t>通用标准</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>达到事先约定技术目标，有可复现验证。与研究报酬可同时领取；同一目标按阶段累计只领一次总额。重大突破另确认，不自动倍增。</t>
+          <t>原先无法解决或未经验证的问题得到解决，并通过可重复验证；能说明解决方法和适用条件。与研究报酬可同时领取；同一目标按阶段累计只领一次总额。重大突破另确认，不自动倍增。须同时满足四项认定条件，详见RD08。</t>
         </is>
       </c>
     </row>
@@ -12871,12 +12871,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>试行参考；立项确认验收指标</t>
+          <t>通用标准</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>设计、BOM、工艺和检验要求交接，首批生产通过约定验收。良率等指标按项目确认，不默认95%。同系列共用方案只计一次。</t>
+          <t>设计、BOM、工艺及检验资料交接完整，首批生产通过验收，关键问题完成处理。良率等指标按项目确认，不默认95%。同系列共用方案只计一次。</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>任务阶段验收</t>
+          <t>研究阶段定义</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -12959,164 +12959,174 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>执行</t>
+          <t>通用标准</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>同一研究任务先定总报酬，再分配独立可验收节点，节点金额合计等于任务总报酬。按已验收节点所在月结算，不要求等整个问题研究结束。</t>
+          <t>研究阶段按实际交付划分，不按周数、试验次数或SKU数量计费。不是每个项目都必须做齐所有阶段。以下为通用参考阶段，结合实际流程选用：</t>
         </is>
       </c>
     </row>
     <row r="14" ht="85" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>RD07</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>阶段示例</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>示例，不是统一单价</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>参考研究任务250元：分析方案50元、关键试验100元、结论与下一步100元。验收前两节点当月付150元，最后节点完成补100元；全任务累计250元。达到独立突破目标另奖500元，项目投产通过验收另奖500元。</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>RS01</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>专利信息调查与风险整理</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>元/阶段</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>通用标准</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>相关专利清单、关键技术内容对照、疑似风险点及待专业确认事项；不能仅凭员工检索就认定没有侵权风险。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="85" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>RD08</t>
+          <t>RS02</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>有效失败与正常试验</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
+          <t>拆机与原理分析</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>250</v>
+      </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>规则</t>
+          <t>元/阶段</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>执行</t>
+          <t>通用标准</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>可靠地排除一条路线可以拿研究报酬。只有事先把判明可行性设为突破目标时，才按约定认定突破。正常探索和有效失败不是责任返工；本人疏漏违反已确认要求造成的返工不另计。</t>
+          <t>拆机记录、零部件清单、关键结构及工作原理说明、尚未解决的问题。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="85" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>RD09</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>周度跟进</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>执行</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>每周一次记录新增成果、当前卡点、下一步，保留已有工作记录。无突破不等于偷懒；无新增证据、反复尝试不总结需复核方法。周报不单独付酬。</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>RS03</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>零部件寻找与适配验证</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>元/阶段</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>通用标准</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>候选零部件比较、来源及规格、适配试验记录、选用或排除结论。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="85" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>RD10</t>
+          <t>RS04</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>延期与调整</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n"/>
+          <t>改型设计与样机验证</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>250</v>
+      </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>规则</t>
+          <t>元/阶段</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>执行</t>
+          <t>通用标准</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>按约定检查点说明障碍、已尝试方法和下一步，负责人决定继续、调整或暂停。合理等待不扣已验收报酬。原表60天终止判断不作为默认，按项目确认检查安排。</t>
+          <t>设计方案、改动依据、样机或关键结构验证、问题及修订记录。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="85" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>RD11</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>研发与运营边界</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>执行</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>按实际工作和交付划分，不以投产前后日期一刀切。研发已付的资料、图稿等复用不重领；实际独立运营上架、图片上传等按运营规则计，不因发生在投产前自动归研发。</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>RS05</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>综合测试与定型</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>元/阶段</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>通用标准</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>按预定要求完成性能、可靠性等测试，整理结果、遗留问题和定型建议。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="85" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>RD12</t>
+          <t>RD07</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>系列及多人合作</t>
+          <t>阶段付款节点</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -13127,58 +13137,62 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
+          <t>通用标准</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>每个250元阶段统一拆成三个付款节点，避免研究一两周却一直拿不到报酬。按已验收节点所在月结算，不要求等整个阶段研究结束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="85" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>分析与验证方案</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
           <t>执行</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>共用研究、突破和投产成果在项目内只计一次；多人分配同一项目总报酬和提成池，份额合计100%。不同SKU不自动构成新研究项目。 例如同一研究任务250元，甲乙按已确认贡献60%/40%分配为150元/100元，不是每人250元；独立上架或其他不同交付仍按对应项目另计。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="85" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>RD13</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>研发提成与运营奖</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>执行</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>产品研发贡献的持续提成与运营人员后续独立改善奖励可以并存。检查是否同一贡献重复奖励，不因同一产品就一律互斥；广告同一效果仍受专项排重规则约束。</t>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>明确问题、已有依据、准备验证什么及如何验证。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="85" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>RD14</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>投产后问题处理</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
+          <t>核心研究与试验</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>150</v>
+      </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>规则</t>
+          <t>元</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -13188,91 +13202,373 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>本人设计责任缺陷的补救不另加研究/突破奖金；新的独立需求或技术问题另确认。原表“3个月质量义务”不作为新增默认承诺，按项目确认责任及支持范围。</t>
+          <t>完成约定的主要调查或试验，有可检查的记录。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="85" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>RD15</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>立项记录</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>字段</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>结论与交付</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>执行</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>项目及任务ID、研究问题、技术目标、交付/验证方法、研究总报酬及节点分配、检查日期、成员份额、突破及投产目标、验收记录、已结算金额。提成另记参数确认和结算记录。 本月应付研究报酬及突破/投产奖金＝已验收累计应付总额减去历史已付金额，只结正差额。</t>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>形成结论、依据、资料及下一步建议。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="85" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>RD16</t>
+          <t>RD08</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>立项金额确认模板</t>
+          <t>突破奖金认定条件</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>通用标准</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>正常完成阶段不自动算作突破。须同时满足四项：①开始研究时已登记明确技术难点和通过标准；②员工提出并落实了解决办法；③通过重复测试或不同样本验证，有记录支持；④解决办法能够用于后续设计、制造或使用。例如，找到常规替代零件属于研究阶段；解决了原来无法兼容的结构问题并验证性能满足要求，才另外奖励500元。同一问题多次改进、反复测试只算一个突破。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>RD09</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>计算示例</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>示例</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>示例</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>完成5个研究阶段：5×250＝1,250元；解决2个独立技术难点：2×500＝1,000元；通过投产验收：500元；项目合计2,750元，按阶段陆续支付。销售提成另算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>RD10</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>三条边界</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>①有效研究失败可以拿阶段报酬；②本人疏漏造成的返工不另付；③同系列、多人共用同一成果，只核一份总报酬再分配。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>RD11</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>有效失败与正常试验</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>可靠地排除一条路线可以拿研究报酬。只有事先把判明可行性设为突破目标时，才按约定认定突破。正常探索和有效失败不是责任返工；本人疏漏违反已确认要求造成的返工不另计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>RD12</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>周度跟进</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>每周一次记录新增成果、当前卡点、下一步，保留已有工作记录。无突破不等于偷懒；无新增证据、反复尝试不总结需复核方法。周报不单独付酬。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>RD13</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>延期与调整</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>按约定检查点说明障碍、已尝试方法和下一步，负责人决定继续、调整或暂停。合理等待不扣已验收报酬。原表60天终止判断不作为默认，按项目确认检查安排。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>RD14</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>研发与运营边界</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>按实际工作和交付划分，不以投产前后日期一刀切。研发已付的资料、图稿等复用不重领；实际独立运营上架、图片上传等按运营规则计，不因发生在投产前自动归研发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>RD15</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>系列及多人合作</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>共用研究、突破和投产成果在项目内只计一次；多人分配同一项目总报酬和提成池，份额合计100%。不同SKU不自动构成新研究项目。 例如同一研究任务250元，甲乙按已确认贡献60%/40%分配为150元/100元，不是每人250元；独立上架或其他不同交付仍按对应项目另计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>RD16</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>研发提成与运营奖</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>产品研发贡献的持续提成与运营人员后续独立改善奖励可以并存。检查是否同一贡献重复奖励，不因同一产品就一律互斥；广告同一效果仍受专项排重规则约束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>RD17</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>投产后问题处理</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>本人设计责任缺陷的补救不另加研究/突破奖金；新的独立需求或技术问题另确认。原表“3个月质量义务”不作为新增默认承诺，按项目确认责任及支持范围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>RD18</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>立项记录</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
           <t>字段</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>执行</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>项目及任务ID、研究问题、技术目标、交付/验证方法、研究总报酬及节点分配、检查日期、成员份额、突破及投产目标、验收记录、已结算金额。提成另记参数确认和结算记录。 本月应付研究报酬及突破/投产奖金＝已验收累计应付总额减去历史已付金额，只结正差额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>RD19</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>立项金额确认模板</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>开始前填写</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>项目ID、独立技术问题、已有资料、需验证的假设、计划验证路线、各节点交付及金额、预计有效投入、检查日期、突破指标及奖金、成员份额、批准人及日期。普通调研和技术研究边界按实际交付判断，不重复领取。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="85" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>RD17</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>阶段工作如何拆</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>执行</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>可按实际技术问题安排权利信息调查、拆机及原理分析、零部件适配验证、改型设计验证。它们可以是一个任务的多个节点，也可能是独立任务；立项先明确，不能看到阶段名称就分别领取250元。有效排除路线可验收研究报酬，未达到独立突破指标不发突破奖。</t>
         </is>
       </c>
     </row>
